--- a/data/trans_camb/P3A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 7,14</t>
+          <t>-16,51; 6,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 10,79</t>
+          <t>-11,53; 11,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,71; 74,47</t>
+          <t>56,97; 75,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 11,65</t>
+          <t>-8,4; 11,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 21,64</t>
+          <t>0,29; 21,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,15; 80,83</t>
+          <t>63,99; 81,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 5,65</t>
+          <t>-9,65; 5,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 13,97</t>
+          <t>-2,18; 13,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,88; 75,07</t>
+          <t>62,38; 75,56</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,24; 39,53</t>
+          <t>-56,62; 34,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,99; 59,74</t>
+          <t>-40,04; 63,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>179,77; 439,92</t>
+          <t>180,2; 446,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,55; 117,59</t>
+          <t>-43,47; 119,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 216,05</t>
+          <t>0,29; 218,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>280,25; 896,22</t>
+          <t>285,03; 907,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 36,02</t>
+          <t>-41,0; 34,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 85,96</t>
+          <t>-10,13; 79,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>254,45; 504,92</t>
+          <t>242,83; 500,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 14,29</t>
+          <t>-11,28; 13,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 16,9</t>
+          <t>-5,75; 17,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,82; 72,36</t>
+          <t>52,68; 71,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 7,7</t>
+          <t>-17,79; 8,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 11,49</t>
+          <t>-14,85; 10,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,26; 64,06</t>
+          <t>42,62; 64,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 7,64</t>
+          <t>-10,99; 6,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 10,74</t>
+          <t>-6,02; 10,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,14; 65,3</t>
+          <t>50,67; 65,17</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 71,06</t>
+          <t>-34,83; 73,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 85,57</t>
+          <t>-18,8; 93,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148,99; 372,9</t>
+          <t>155,37; 384,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,55; 25,72</t>
+          <t>-41,85; 33,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 40,01</t>
+          <t>-33,65; 36,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,05; 234,58</t>
+          <t>94,55; 236,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 28,35</t>
+          <t>-31,28; 23,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 41,68</t>
+          <t>-17,06; 39,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133,2; 250,37</t>
+          <t>132,88; 250,96</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 21,06</t>
+          <t>0,34; 20,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 18,16</t>
+          <t>-5,99; 16,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48,62; 73,38</t>
+          <t>49,61; 73,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 6,83</t>
+          <t>-14,98; 8,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 3,5</t>
+          <t>-18,6; 3,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,07; 66,36</t>
+          <t>38,23; 64,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 10,25</t>
+          <t>-5,41; 10,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 6,34</t>
+          <t>-8,79; 6,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,14; 65,07</t>
+          <t>47,9; 66,38</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 309,41</t>
+          <t>-3,74; 297,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,45; 304,28</t>
+          <t>-43,06; 228,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>255,01; 1209,34</t>
+          <t>287,62; 1218,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 41,33</t>
+          <t>-54,93; 46,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,73; 19,47</t>
+          <t>-67,38; 19,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>135,86; 393,88</t>
+          <t>129,56; 353,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 69,53</t>
+          <t>-26,27; 71,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,74; 42,67</t>
+          <t>-40,86; 46,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>211,62; 445,99</t>
+          <t>210,25; 485,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 9,97</t>
+          <t>-9,07; 9,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 7,54</t>
+          <t>-8,13; 7,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,74; 57,53</t>
+          <t>38,73; 57,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 8,34</t>
+          <t>-8,4; 8,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 8,26</t>
+          <t>-8,23; 9,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,4; 65,99</t>
+          <t>51,58; 65,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 6,8</t>
+          <t>-5,71; 6,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 5,85</t>
+          <t>-5,45; 6,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>46,9; 59,94</t>
+          <t>48,07; 59,9</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 35,94</t>
+          <t>-24,17; 32,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 25,05</t>
+          <t>-21,39; 26,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100,84; 202,08</t>
+          <t>99,64; 201,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 33,5</t>
+          <t>-25,27; 35,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 33,55</t>
+          <t>-24,44; 37,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>146,06; 276,86</t>
+          <t>149,65; 279,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 23,23</t>
+          <t>-16,81; 22,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 20,7</t>
+          <t>-16,06; 22,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>132,01; 218,19</t>
+          <t>134,67; 216,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 4,4</t>
+          <t>-20,19; 5,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 0,55</t>
+          <t>-22,18; 2,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,14; 51,46</t>
+          <t>30,5; 50,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 12,75</t>
+          <t>-11,22; 12,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 4,95</t>
+          <t>-18,87; 4,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,1; 42,09</t>
+          <t>22,75; 42,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 5,74</t>
+          <t>-12,55; 5,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-17,44; -0,48</t>
+          <t>-16,94; -0,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28,53; 43,51</t>
+          <t>29,07; 43,68</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 10,05</t>
+          <t>-37,42; 14,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 1,86</t>
+          <t>-39,84; 4,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55,15; 134,46</t>
+          <t>53,21; 128,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 27,3</t>
+          <t>-19,28; 29,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,15; 11,09</t>
+          <t>-32,79; 10,31</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,25; 95,18</t>
+          <t>38,87; 97,53</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 12,81</t>
+          <t>-22,99; 11,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-32,03; -1,11</t>
+          <t>-30,89; 0,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>50,39; 97,95</t>
+          <t>52,15; 98,6</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 11,53</t>
+          <t>-16,44; 11,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-36,69; -9,2</t>
+          <t>-35,3; -9,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8,23; 31,48</t>
+          <t>8,07; 31,45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 0,24</t>
+          <t>-25,59; 0,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-33,33; -4,3</t>
+          <t>-31,76; -2,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,91; 34,41</t>
+          <t>10,0; 34,41</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 0,72</t>
+          <t>-18,61; 0,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-29,44; -9,88</t>
+          <t>-30,16; -10,13</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12,54; 28,74</t>
+          <t>12,1; 28,69</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 19,53</t>
+          <t>-23,07; 19,4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-52,13; -14,59</t>
+          <t>-50,23; -14,39</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11,54; 54,2</t>
+          <t>11,21; 54,16</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-37,61; 0,17</t>
+          <t>-37,05; 0,15</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -8,04</t>
+          <t>-46,22; -4,84</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,95; 63,56</t>
+          <t>13,88; 63,7</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 1,14</t>
+          <t>-27,21; 0,52</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-43,65; -16,81</t>
+          <t>-44,15; -16,05</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17,81; 48,26</t>
+          <t>18,02; 48,34</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 4,27</t>
+          <t>-5,89; 3,96</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 2,22</t>
+          <t>-7,75; 2,03</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45,71; 54,84</t>
+          <t>45,63; 54,63</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 2,42</t>
+          <t>-6,38; 2,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 1,88</t>
+          <t>-7,46; 1,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,42; 54,69</t>
+          <t>46,56; 54,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 2,02</t>
+          <t>-5,14; 1,92</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 0,85</t>
+          <t>-6,44; 0,32</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>47,7; 53,64</t>
+          <t>47,68; 53,54</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 13,05</t>
+          <t>-15,47; 11,67</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 6,72</t>
+          <t>-20,58; 6,12</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>119,09; 170,12</t>
+          <t>119,69; 170,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 7,29</t>
+          <t>-17,05; 8,94</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 5,87</t>
+          <t>-19,47; 5,13</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>118,92; 166,21</t>
+          <t>120,86; 168,53</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 5,79</t>
+          <t>-13,97; 5,7</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 2,37</t>
+          <t>-17,54; 0,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>127,89; 162,12</t>
+          <t>127,53; 160,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 6,3</t>
+          <t>-15,49; 6,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 11,76</t>
+          <t>-11,26; 12,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,97; 75,25</t>
+          <t>55,22; 74,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 11,87</t>
+          <t>-7,48; 13,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 21,42</t>
+          <t>1,36; 23,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,99; 81,34</t>
+          <t>64,47; 81,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 5,14</t>
+          <t>-9,66; 5,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 13,3</t>
+          <t>-2,44; 13,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,38; 75,56</t>
+          <t>62,32; 75,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,62; 34,06</t>
+          <t>-53,45; 32,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 63,36</t>
+          <t>-37,78; 70,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>180,2; 446,07</t>
+          <t>169,49; 442,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 119,05</t>
+          <t>-39,03; 137,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 218,99</t>
+          <t>6,0; 258,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>285,03; 907,06</t>
+          <t>279,74; 824,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,0; 34,35</t>
+          <t>-40,62; 32,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 79,88</t>
+          <t>-10,79; 88,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>242,83; 500,76</t>
+          <t>240,68; 485,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 13,71</t>
+          <t>-11,36; 14,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 17,92</t>
+          <t>-5,81; 17,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,68; 71,86</t>
+          <t>53,0; 73,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 8,86</t>
+          <t>-18,66; 7,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 10,26</t>
+          <t>-13,15; 10,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,62; 64,41</t>
+          <t>43,6; 63,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 6,53</t>
+          <t>-11,56; 6,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 10,29</t>
+          <t>-5,77; 10,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,67; 65,17</t>
+          <t>50,8; 65,34</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 73,21</t>
+          <t>-36,14; 74,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 93,46</t>
+          <t>-17,71; 92,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155,37; 384,15</t>
+          <t>151,09; 386,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 33,35</t>
+          <t>-44,08; 25,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 36,91</t>
+          <t>-29,99; 35,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,55; 236,27</t>
+          <t>95,49; 224,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,28; 23,48</t>
+          <t>-31,57; 25,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 39,07</t>
+          <t>-16,0; 40,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>132,88; 250,96</t>
+          <t>139,45; 258,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 20,54</t>
+          <t>-0,07; 20,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 16,07</t>
+          <t>-4,36; 17,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49,61; 73,92</t>
+          <t>46,82; 73,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 8,03</t>
+          <t>-14,47; 7,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 3,44</t>
+          <t>-18,36; 4,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,23; 64,19</t>
+          <t>39,76; 64,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 10,19</t>
+          <t>-4,75; 10,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 6,3</t>
+          <t>-9,81; 5,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47,9; 66,38</t>
+          <t>47,39; 65,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 297,81</t>
+          <t>-6,87; 295,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,06; 228,42</t>
+          <t>-32,56; 244,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>287,62; 1218,26</t>
+          <t>269,09; 1168,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,93; 46,96</t>
+          <t>-52,0; 41,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,38; 19,89</t>
+          <t>-64,55; 24,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>129,56; 353,41</t>
+          <t>133,37; 372,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 71,67</t>
+          <t>-21,36; 72,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 46,22</t>
+          <t>-44,86; 36,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>210,25; 485,46</t>
+          <t>207,43; 478,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 9,9</t>
+          <t>-7,65; 10,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 7,87</t>
+          <t>-8,91; 8,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,73; 57,68</t>
+          <t>39,11; 58,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 8,73</t>
+          <t>-8,14; 7,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 9,43</t>
+          <t>-7,85; 8,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,58; 65,88</t>
+          <t>51,32; 65,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 6,52</t>
+          <t>-6,06; 6,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 6,28</t>
+          <t>-5,96; 5,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,07; 59,9</t>
+          <t>48,3; 59,14</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 32,94</t>
+          <t>-20,21; 36,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 26,63</t>
+          <t>-23,46; 29,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99,64; 201,64</t>
+          <t>103,31; 205,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 35,78</t>
+          <t>-24,34; 31,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 37,22</t>
+          <t>-23,78; 35,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>149,65; 279,88</t>
+          <t>148,1; 272,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 22,82</t>
+          <t>-17,02; 22,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 22,16</t>
+          <t>-17,01; 19,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>134,67; 216,2</t>
+          <t>135,22; 212,93</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 5,7</t>
+          <t>-20,92; 5,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 2,04</t>
+          <t>-23,86; 2,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30,5; 50,94</t>
+          <t>29,35; 51,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 12,89</t>
+          <t>-11,47; 12,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 4,59</t>
+          <t>-20,03; 4,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,75; 42,36</t>
+          <t>21,18; 41,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 5,24</t>
+          <t>-12,25; 6,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -0,02</t>
+          <t>-17,85; 0,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,07; 43,68</t>
+          <t>29,54; 44,5</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-37,42; 14,08</t>
+          <t>-38,01; 15,98</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,84; 4,42</t>
+          <t>-42,19; 5,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53,21; 128,99</t>
+          <t>49,87; 127,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 29,13</t>
+          <t>-18,6; 28,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 10,31</t>
+          <t>-33,9; 10,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,87; 97,53</t>
+          <t>35,85; 95,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 11,41</t>
+          <t>-22,17; 13,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-30,89; 0,17</t>
+          <t>-32,67; 0,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>52,15; 98,6</t>
+          <t>52,86; 100,32</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 11,64</t>
+          <t>-17,4; 11,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-35,3; -9,12</t>
+          <t>-34,9; -8,38</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8,07; 31,45</t>
+          <t>7,62; 31,16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 0,06</t>
+          <t>-25,85; 0,12</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-31,76; -2,46</t>
+          <t>-31,15; -4,72</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,0; 34,41</t>
+          <t>9,82; 32,38</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 0,3</t>
+          <t>-18,85; 0,32</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-30,16; -10,13</t>
+          <t>-30,0; -11,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12,1; 28,69</t>
+          <t>11,62; 29,38</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 19,4</t>
+          <t>-24,48; 18,5</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-50,23; -14,39</t>
+          <t>-49,68; -13,8</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11,21; 54,16</t>
+          <t>10,79; 54,92</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-37,05; 0,15</t>
+          <t>-37,11; 0,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,22; -4,84</t>
+          <t>-46,03; -7,55</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,88; 63,7</t>
+          <t>14,18; 57,35</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 0,52</t>
+          <t>-27,76; 0,65</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-44,15; -16,05</t>
+          <t>-44,37; -18,46</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>18,02; 48,34</t>
+          <t>17,02; 50,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,96</t>
+          <t>-6,3; 3,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 2,03</t>
+          <t>-7,63; 1,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45,63; 54,63</t>
+          <t>45,51; 54,56</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 2,85</t>
+          <t>-7,34; 2,48</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,76</t>
+          <t>-7,1; 2,4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,56; 54,67</t>
+          <t>46,16; 54,56</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 1,92</t>
+          <t>-5,02; 2,05</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 0,32</t>
+          <t>-5,98; 0,86</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>47,68; 53,54</t>
+          <t>47,39; 53,69</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 11,67</t>
+          <t>-16,18; 10,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,58; 6,12</t>
+          <t>-20,45; 6,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>119,69; 170,57</t>
+          <t>119,64; 170,14</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 8,94</t>
+          <t>-18,96; 7,54</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 5,13</t>
+          <t>-18,79; 7,23</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>120,86; 168,53</t>
+          <t>118,49; 165,03</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 5,7</t>
+          <t>-13,47; 6,11</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 0,93</t>
+          <t>-16,27; 2,27</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>127,53; 160,81</t>
+          <t>125,22; 160,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,41</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>72,3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-4,86</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,04</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>65,84</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,41</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,3</t>
+          <t>66,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69,21</t>
+          <t>68,79</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 6,22</t>
+          <t>-8,9; 11,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 12,22</t>
+          <t>-0,3; 21,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,22; 74,88</t>
+          <t>63,03; 80,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 13,22</t>
+          <t>-15,6; 7,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 23,43</t>
+          <t>-11,66; 10,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,47; 81,18</t>
+          <t>56,95; 74,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 5,37</t>
+          <t>-9,73; 5,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 13,42</t>
+          <t>-2,26; 13,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62,32; 75,36</t>
+          <t>62,28; 75,02</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75,42%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>477,78%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-20,18%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>273,14%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>75,42%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>484,4%</t>
+          <t>273,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>348,16%</t>
+          <t>346,06%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 32,47</t>
+          <t>-42,55; 117,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 70,59</t>
+          <t>-5,41; 216,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>169,49; 442,81</t>
+          <t>276,72; 883,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 137,76</t>
+          <t>-54,24; 39,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 258,07</t>
+          <t>-40,99; 59,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>279,74; 824,28</t>
+          <t>180,38; 440,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,62; 32,98</t>
+          <t>-40,98; 36,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 88,89</t>
+          <t>-9,85; 85,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>240,68; 485,17</t>
+          <t>249,7; 501,7</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-5,55</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,62</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53,7</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,21</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,75</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>63,69</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,55</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,83</t>
+          <t>63,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>58,8</t>
+          <t>58,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 14,14</t>
+          <t>-18,86; 7,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 17,68</t>
+          <t>-13,98; 11,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,0; 73,15</t>
+          <t>41,74; 63,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 7,92</t>
+          <t>-9,47; 14,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 10,7</t>
+          <t>-6,47; 16,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,6; 63,4</t>
+          <t>52,4; 72,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 6,68</t>
+          <t>-10,47; 7,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 10,69</t>
+          <t>-6,32; 10,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,8; 65,34</t>
+          <t>49,79; 65,04</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-15,29%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-4,45%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>147,84%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,59%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>21,81%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>241,78%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-15,29%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-4,45%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>148,21%</t>
+          <t>240,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>187,94%</t>
+          <t>187,26%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,14; 74,0</t>
+          <t>-44,55; 25,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 92,59</t>
+          <t>-31,64; 40,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151,09; 386,02</t>
+          <t>93,66; 235,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 25,28</t>
+          <t>-30,28; 71,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 35,15</t>
+          <t>-19,89; 85,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,49; 224,59</t>
+          <t>147,3; 370,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 25,49</t>
+          <t>-29,24; 28,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 40,67</t>
+          <t>-17,8; 41,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>139,45; 258,56</t>
+          <t>132,46; 249,37</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-3,97</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-7,35</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56,11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>10,88</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>5,45</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>62,48</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,97</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-7,35</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53,65</t>
+          <t>61,71</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57,13</t>
+          <t>57,89</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 20,19</t>
+          <t>-15,19; 6,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 17,45</t>
+          <t>-17,95; 3,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,82; 73,2</t>
+          <t>43,97; 68,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 7,47</t>
+          <t>0,57; 21,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 4,05</t>
+          <t>-4,37; 18,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,76; 64,94</t>
+          <t>47,18; 72,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 10,17</t>
+          <t>-5,32; 10,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 5,83</t>
+          <t>-9,38; 6,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47,39; 65,64</t>
+          <t>49,35; 66,13</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-16,83%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-31,13%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>237,77%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>96,85%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>48,56%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>556,45%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-16,83%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-31,13%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>227,35%</t>
+          <t>549,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>308,3%</t>
+          <t>312,42%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 295,53</t>
+          <t>-53,42; 41,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 244,89</t>
+          <t>-62,73; 19,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>269,09; 1168,06</t>
+          <t>144,71; 396,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,0; 41,93</t>
+          <t>-2,25; 309,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,55; 24,02</t>
+          <t>-34,45; 304,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>133,37; 372,16</t>
+          <t>251,61; 1205,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 72,19</t>
+          <t>-24,13; 69,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,86; 36,74</t>
+          <t>-43,74; 42,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>207,43; 478,52</t>
+          <t>213,28; 456,92</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,57</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>57,77</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,24</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>49,11</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,57</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,6</t>
+          <t>51,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>53,83</t>
+          <t>54,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 10,42</t>
+          <t>-8,76; 8,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 8,51</t>
+          <t>-8,28; 8,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,11; 58,41</t>
+          <t>50,48; 65,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 7,94</t>
+          <t>-8,11; 9,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 8,54</t>
+          <t>-9,11; 7,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,32; 65,31</t>
+          <t>44,23; 58,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 6,49</t>
+          <t>-5,86; 6,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 5,59</t>
+          <t>-6,32; 5,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,3; 59,14</t>
+          <t>49,09; 60,01</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>196,65%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-0,7%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>144,96%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>199,49%</t>
+          <t>153,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>170,1%</t>
+          <t>173,28%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 36,41</t>
+          <t>-26,59; 33,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,46; 29,66</t>
+          <t>-23,88; 33,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>103,31; 205,45</t>
+          <t>143,92; 274,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 31,16</t>
+          <t>-22,41; 35,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 35,79</t>
+          <t>-23,83; 25,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>148,1; 272,82</t>
+          <t>112,57; 206,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 22,27</t>
+          <t>-17,14; 23,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 19,57</t>
+          <t>-17,92; 20,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>135,22; 212,93</t>
+          <t>136,37; 216,98</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,97</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-7,16</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>32,0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-8,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-10,47</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>41,29</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,97</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-7,16</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,81</t>
+          <t>41,18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>36,49</t>
+          <t>36,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 5,78</t>
+          <t>-12,19; 12,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 2,17</t>
+          <t>-18,78; 4,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,35; 51,56</t>
+          <t>20,64; 41,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 12,67</t>
+          <t>-20,81; 4,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 4,64</t>
+          <t>-22,55; 0,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,18; 41,64</t>
+          <t>31,1; 51,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 6,36</t>
+          <t>-12,04; 5,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 0,15</t>
+          <t>-17,44; -0,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,54; 44,5</t>
+          <t>28,14; 43,21</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-13,79%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>61,62%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-16,46%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-21,54%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>84,97%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-13,79%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 15,98</t>
+          <t>-20,99; 27,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 5,8</t>
+          <t>-32,15; 11,09</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>49,87; 127,51</t>
+          <t>35,48; 93,25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 28,17</t>
+          <t>-37,27; 10,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 10,2</t>
+          <t>-41,01; 1,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,85; 95,12</t>
+          <t>55,13; 135,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 13,75</t>
+          <t>-22,43; 12,81</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 0,04</t>
+          <t>-32,03; -1,11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>52,86; 100,32</t>
+          <t>49,78; 96,8</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-13,13</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-18,74</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>22,66</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-2,04</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-22,23</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>19,65</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-13,13</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-18,74</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,94</t>
+          <t>19,04</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20,78</t>
+          <t>20,82</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 11,0</t>
+          <t>-26,14; 0,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-34,9; -8,38</t>
+          <t>-33,33; -4,3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7,62; 31,16</t>
+          <t>11,46; 35,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 0,12</t>
+          <t>-15,62; 11,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-31,15; -4,72</t>
+          <t>-36,69; -9,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,82; 32,38</t>
+          <t>6,98; 30,84</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 0,32</t>
+          <t>-19,14; 0,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-30,0; -11,07</t>
+          <t>-29,44; -9,88</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11,62; 29,38</t>
+          <t>12,68; 28,68</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-20,68%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-29,5%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>35,67%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-3,1%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-33,85%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>29,93%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-20,68%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-29,5%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 18,5</t>
+          <t>-37,61; 0,17</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-49,68; -13,8</t>
+          <t>-47,48; -8,04</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10,79; 54,92</t>
+          <t>16,5; 64,53</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 0,57</t>
+          <t>-21,47; 19,53</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,03; -7,55</t>
+          <t>-52,13; -14,59</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,18; 57,35</t>
+          <t>10,41; 53,85</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 0,65</t>
+          <t>-27,93; 1,14</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-44,37; -18,46</t>
+          <t>-43,65; -16,81</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17,02; 50,1</t>
+          <t>18,03; 48,42</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-2,12</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-2,56</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>50,48</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-1,05</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,79</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>50,45</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-2,56</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,78</t>
+          <t>51,23</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>50,63</t>
+          <t>50,84</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 3,55</t>
+          <t>-6,92; 2,42</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 1,99</t>
+          <t>-7,22; 1,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>45,51; 54,56</t>
+          <t>46,35; 54,61</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 2,48</t>
+          <t>-6,08; 4,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 2,4</t>
+          <t>-7,37; 2,22</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,16; 54,56</t>
+          <t>47,11; 55,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 2,05</t>
+          <t>-4,98; 2,02</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 0,86</t>
+          <t>-5,84; 0,85</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>47,39; 53,69</t>
+          <t>48,04; 53,78</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-5,95%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-7,18%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>141,4%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-2,96%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-7,88%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>142,45%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-5,95%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-7,18%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>142,25%</t>
+          <t>144,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>142,38%</t>
+          <t>142,95%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 10,7</t>
+          <t>-17,89; 7,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 6,17</t>
+          <t>-18,64; 5,87</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>119,64; 170,14</t>
+          <t>118,26; 165,32</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 7,54</t>
+          <t>-15,87; 13,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 7,23</t>
+          <t>-19,42; 6,72</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>118,49; 165,03</t>
+          <t>122,34; 172,4</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 6,11</t>
+          <t>-13,37; 5,79</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 2,27</t>
+          <t>-15,75; 2,37</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>125,22; 160,25</t>
+          <t>128,86; 162,29</t>
         </is>
       </c>
     </row>
